--- a/data/lexicon_reviewed/Moroccan_reviewed.xlsx
+++ b/data/lexicon_reviewed/Moroccan_reviewed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mbzuaiac-my.sharepoint.com/personal/amr_keleg_mbzuai_ac_ae/Documents/projects/arabizi-across-dialects/data/lexicon_reviewed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_E432A62F7053088059B170545B25EE01649EF6BF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDD959B7-757A-A942-8C77-630B3ED12CD1}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_E432A62F7053088059B170545B25EE01649EF6BF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED30DE1-41E7-A84F-9955-7F2968722D2F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="459">
   <si>
     <t>Word</t>
   </si>
@@ -26975,7 +26975,9 @@
       <c r="A746" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B746" s="11"/>
+      <c r="B746" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C746" s="11"/>
       <c r="D746" s="11"/>
       <c r="E746" s="11"/>
@@ -27379,7 +27381,9 @@
       <c r="A758" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B758" s="11"/>
+      <c r="B758" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C758" s="11"/>
       <c r="D758" s="11"/>
       <c r="E758" s="11"/>
@@ -27561,7 +27565,9 @@
       <c r="A764" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B764" s="11"/>
+      <c r="B764" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C764" s="11"/>
       <c r="D764" s="11"/>
       <c r="E764" s="11"/>
@@ -30169,7 +30175,9 @@
       <c r="A842" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="B842" s="13"/>
+      <c r="B842" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C842" s="13"/>
       <c r="D842" s="13"/>
       <c r="E842" s="13"/>
@@ -31093,7 +31101,9 @@
       <c r="A872" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="B872" s="11"/>
+      <c r="B872" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="C872" s="11"/>
       <c r="D872" s="11"/>
       <c r="E872" s="11"/>
@@ -31467,7 +31477,9 @@
       <c r="A884" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="B884" s="15"/>
+      <c r="B884" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="C884" s="15" t="s">
         <v>59</v>
       </c>
